--- a/clutch_score_analysis.xlsx
+++ b/clutch_score_analysis.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2754,6 +2754,41 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Tyler</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Bethpage Blue</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="E67" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-1.972</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/clutch_score_analysis.xlsx
+++ b/clutch_score_analysis.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2789,6 +2789,41 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Tyler</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Brentwood Country Club</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>2</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Solid Finish</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/clutch_score_analysis.xlsx
+++ b/clutch_score_analysis.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1112,35 +1112,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Rich</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45453</v>
+        <v>46173</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.2</v>
+        <v>1.267</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="G20" t="n">
-        <v>2.556</v>
+        <v>0.978</v>
       </c>
       <c r="H20" t="n">
-        <v>0.027</v>
+        <v>-0.014</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -1151,27 +1151,27 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45492</v>
+        <v>45453</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brentwood Country Club</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.067</v>
+        <v>2.2</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="G21" t="n">
-        <v>5.894</v>
+        <v>2.556</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.122</v>
+        <v>0.027</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45520</v>
+        <v>45492</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Middle Island Country Club - Oak and Spruce</t>
+          <t>Brentwood Country Club</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.4</v>
+        <v>2.067</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8</v>
+        <v>5.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.139</v>
+        <v>5.894</v>
       </c>
       <c r="H22" t="n">
-        <v>0.046</v>
+        <v>-0.122</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1221,31 +1221,31 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45765</v>
+        <v>45520</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cherry Creek</t>
+          <t>Middle Island Country Club - Oak and Spruce</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>3.2</v>
+        <v>-1.8</v>
       </c>
       <c r="G23" t="n">
-        <v>3.817</v>
+        <v>-2.139</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.105</v>
+        <v>0.046</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -1256,31 +1256,31 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45853</v>
+        <v>45765</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pine Hollow</t>
+          <t>Cherry Creek</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.067</v>
+        <v>2.4</v>
       </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8</v>
+        <v>3.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.25</v>
+        <v>3.817</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.014</v>
+        <v>-0.105</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1291,62 +1291,62 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45894</v>
+        <v>45853</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Pine Hollow</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2.4</v>
+        <v>2.067</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
-        <v>2.2</v>
+        <v>-0.8</v>
       </c>
       <c r="G25" t="n">
-        <v>3.3</v>
+        <v>-1.25</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.046</v>
+        <v>-0.014</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45048</v>
+        <v>45894</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1.333</v>
+        <v>2.4</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="G26" t="n">
-        <v>2.183</v>
+        <v>3.3</v>
       </c>
       <c r="H26" t="n">
-        <v>0.01</v>
+        <v>-0.046</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1361,27 +1361,27 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45050</v>
+        <v>45048</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.067</v>
+        <v>1.333</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>1.556</v>
+        <v>2.183</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.023</v>
+        <v>0.01</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45053</v>
+        <v>45050</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1407,20 +1407,20 @@
         <v>1.067</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.8</v>
+        <v>1.2</v>
       </c>
       <c r="G28" t="n">
-        <v>-2.361</v>
+        <v>1.556</v>
       </c>
       <c r="H28" t="n">
-        <v>0.098</v>
+        <v>-0.023</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1435,27 +1435,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bethpage Yellow</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1.4</v>
+        <v>1.067</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>2.2</v>
+        <v>-1.8</v>
       </c>
       <c r="G29" t="n">
-        <v>2.939</v>
+        <v>-2.361</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.079</v>
+        <v>0.098</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -1466,27 +1466,27 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45084</v>
+        <v>45053</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Bethpage Yellow</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.133</v>
+        <v>1.4</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="G30" t="n">
-        <v>1.733</v>
+        <v>2.939</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.055</v>
+        <v>-0.079</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1501,31 +1501,31 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45137</v>
+        <v>45084</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bethpage Yellow</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.133</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="G31" t="n">
-        <v>1.283</v>
+        <v>1.733</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.006</v>
+        <v>-0.055</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45143</v>
+        <v>45137</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1544,23 +1544,23 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.067</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="G32" t="n">
-        <v>2.65</v>
+        <v>1.283</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.006</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -1571,31 +1571,31 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45144</v>
+        <v>45143</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bethpage Black</t>
+          <t>Bethpage Yellow</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1.6</v>
+        <v>1.067</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="G33" t="n">
-        <v>1.433</v>
+        <v>2.65</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.06</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1606,31 +1606,31 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45156</v>
+        <v>45144</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Middle Island Country Club - Oak and Spruce</t>
+          <t>Bethpage Black</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1.267</v>
+        <v>1.6</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F34" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="G34" t="n">
-        <v>3.972</v>
+        <v>1.433</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.062</v>
+        <v>-0.06</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -1641,31 +1641,31 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45172</v>
+        <v>45156</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Middle Island Country Club - Oak and Spruce</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.8</v>
+        <v>1.267</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.6</v>
+        <v>2.8</v>
       </c>
       <c r="G35" t="n">
-        <v>-2.111</v>
+        <v>3.972</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.014</v>
+        <v>-0.062</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1676,31 +1676,31 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45434</v>
+        <v>45172</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bethpage Yellow</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="G36" t="n">
-        <v>0.161</v>
+        <v>-2.111</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.014</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45440</v>
+        <v>45434</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1719,23 +1719,23 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.067</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>2.939</v>
+        <v>0.161</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.04</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1746,27 +1746,27 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45443</v>
+        <v>45440</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Yellow</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1.133</v>
+        <v>1.067</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="G38" t="n">
-        <v>4.128</v>
+        <v>2.939</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1781,31 +1781,31 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45453</v>
+        <v>45443</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1.333</v>
+        <v>1.133</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="G39" t="n">
-        <v>0.239</v>
+        <v>4.128</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.025</v>
+        <v>-0.09</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1816,31 +1816,31 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45465</v>
+        <v>45453</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-2.367</v>
+        <v>0.239</v>
       </c>
       <c r="H40" t="n">
-        <v>0.022</v>
+        <v>-0.025</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1851,31 +1851,31 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45466</v>
+        <v>45465</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bethpage Red</t>
+          <t>Wind Watch Hamlet Course</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.667</v>
+        <v>1.4</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>-1.8</v>
       </c>
       <c r="G41" t="n">
-        <v>1.383</v>
+        <v>-2.367</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.011</v>
+        <v>0.022</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -1886,31 +1886,31 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45467</v>
+        <v>45466</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Bethpage Red</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.533</v>
+        <v>0.667</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>2.033</v>
+        <v>1.383</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.011</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45475</v>
+        <v>45467</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1929,23 +1929,23 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.2</v>
+        <v>0.533</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.4</v>
+        <v>1.6</v>
       </c>
       <c r="G43" t="n">
-        <v>-1.517</v>
+        <v>2.033</v>
       </c>
       <c r="H43" t="n">
-        <v>0.024</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1956,31 +1956,31 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45480</v>
+        <v>45475</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bethpage Red</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.667</v>
+        <v>0.2</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>-1.4</v>
       </c>
       <c r="G44" t="n">
-        <v>2.494</v>
+        <v>-1.517</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.039</v>
+        <v>0.024</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -1991,31 +1991,31 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45487</v>
+        <v>45480</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Red</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.017</v>
+        <v>2.494</v>
       </c>
       <c r="H45" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.039</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -2026,31 +2026,31 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45492</v>
+        <v>45487</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brentwood Country Club</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="G46" t="n">
-        <v>1.35</v>
+        <v>-0.017</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.018</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45496</v>
+        <v>45492</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2069,23 +2069,23 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.467</v>
+        <v>0.667</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>1.783</v>
+        <v>1.35</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.011</v>
+        <v>-0.018</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2096,31 +2096,31 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>45502</v>
+        <v>45496</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Brentwood Country Club</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.533</v>
+        <v>0.467</v>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.4</v>
+        <v>1.4</v>
       </c>
       <c r="G48" t="n">
-        <v>-3.428</v>
+        <v>1.783</v>
       </c>
       <c r="H48" t="n">
-        <v>0.054</v>
+        <v>-0.011</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -2131,31 +2131,31 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>45514</v>
+        <v>45502</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brentwood Country Club</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.867</v>
+        <v>0.533</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
-        <v>2.6</v>
+        <v>-2.4</v>
       </c>
       <c r="G49" t="n">
-        <v>3.278</v>
+        <v>-3.428</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.054</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2166,31 +2166,31 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>45535</v>
+        <v>45514</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bethpage Yellow</t>
+          <t>Brentwood Country Club</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.867</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="G50" t="n">
-        <v>1.011</v>
+        <v>3.278</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.05</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -2201,31 +2201,31 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45570</v>
+        <v>45535</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Yellow</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.4</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E51" t="n">
         <v>2</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.8</v>
+        <v>0.8</v>
       </c>
       <c r="G51" t="n">
-        <v>-1.1</v>
+        <v>1.011</v>
       </c>
       <c r="H51" t="n">
-        <v>0.035</v>
+        <v>-0.05</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2236,31 +2236,31 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>45580</v>
+        <v>45570</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sebonack Golf Club</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>-0.8</v>
       </c>
       <c r="G52" t="n">
-        <v>1.056</v>
+        <v>-1.1</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.013</v>
+        <v>0.035</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2271,31 +2271,31 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45649</v>
+        <v>45580</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ka'anapali Golf Resort Royal Course</t>
+          <t>Sebonack Golf Club</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.2</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.289</v>
+        <v>1.056</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.028</v>
+        <v>-0.013</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2306,31 +2306,31 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45653</v>
+        <v>45649</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Ka'anapali Golf Resort Royal Course</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.4</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.844</v>
+        <v>-0.289</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.012</v>
+        <v>-0.028</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2341,31 +2341,31 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>45655</v>
+        <v>45653</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>1.4</v>
+        <v>-0.8</v>
       </c>
       <c r="G55" t="n">
-        <v>1.989</v>
+        <v>-0.844</v>
       </c>
       <c r="H55" t="n">
-        <v>0.003</v>
+        <v>-0.012</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2376,31 +2376,31 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>45735</v>
+        <v>45655</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.333</v>
+        <v>0.8</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G56" t="n">
-        <v>1.189</v>
+        <v>1.989</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.051</v>
+        <v>0.003</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -2411,27 +2411,27 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>45829</v>
+        <v>45735</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brentwood Country Club</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.267</v>
+        <v>0.333</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0.911</v>
+        <v>1.189</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.033</v>
+        <v>-0.051</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2446,27 +2446,27 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>45831</v>
+        <v>45829</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Brentwood Country Club</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.4</v>
+        <v>0.267</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="G58" t="n">
-        <v>1.483</v>
+        <v>0.911</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.068</v>
+        <v>-0.033</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2481,27 +2481,27 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>45844</v>
+        <v>45831</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="G59" t="n">
-        <v>0.628</v>
+        <v>1.483</v>
       </c>
       <c r="H59" t="n">
-        <v>0.027</v>
+        <v>-0.068</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>45857</v>
+        <v>45844</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2524,23 +2524,23 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.2</v>
+        <v>0.467</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.433</v>
+        <v>0.628</v>
       </c>
       <c r="H60" t="n">
-        <v>0.002</v>
+        <v>0.027</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2551,31 +2551,31 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>45868</v>
+        <v>45857</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bethpage Red</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.667</v>
+        <v>0.2</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>-0.4</v>
       </c>
       <c r="G61" t="n">
-        <v>1.439</v>
+        <v>-0.433</v>
       </c>
       <c r="H61" t="n">
-        <v>0.018</v>
+        <v>0.002</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2586,31 +2586,31 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>45886</v>
+        <v>45868</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spring Lake Thunderbird</t>
+          <t>Bethpage Red</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.2</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.644</v>
+        <v>1.439</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.005</v>
+        <v>0.018</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>45892</v>
+        <v>45886</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2629,23 +2629,23 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.733</v>
+        <v>0.6</v>
       </c>
       <c r="E63" t="n">
         <v>2</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="G63" t="n">
-        <v>0.361</v>
+        <v>-0.644</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.055</v>
+        <v>-0.005</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2656,31 +2656,31 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>45894</v>
+        <v>45892</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1.2</v>
+        <v>0.733</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
-        <v>-2.4</v>
+        <v>0.2</v>
       </c>
       <c r="G64" t="n">
-        <v>-2.606</v>
+        <v>0.361</v>
       </c>
       <c r="H64" t="n">
-        <v>0.068</v>
+        <v>-0.055</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2691,27 +2691,27 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>45897</v>
+        <v>45894</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spring Lake Thunderbird</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.867</v>
+        <v>1.2</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.4</v>
+        <v>-2.4</v>
       </c>
       <c r="G65" t="n">
-        <v>-1.789</v>
+        <v>-2.606</v>
       </c>
       <c r="H65" t="n">
-        <v>0.001</v>
+        <v>0.068</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -2726,27 +2726,27 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>45941</v>
+        <v>45897</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.867</v>
       </c>
       <c r="E66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F66" t="n">
-        <v>-2.2</v>
+        <v>-1.4</v>
       </c>
       <c r="G66" t="n">
-        <v>-2.9</v>
+        <v>-1.789</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -2761,27 +2761,27 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46160</v>
+        <v>45941</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Wind Watch Hamlet Course</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.467</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.6</v>
+        <v>-2.2</v>
       </c>
       <c r="G67" t="n">
-        <v>-1.972</v>
+        <v>-2.9</v>
       </c>
       <c r="H67" t="n">
-        <v>0.029</v>
+        <v>-0.001</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -2796,31 +2796,101 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Bethpage Blue</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-1.972</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tyler</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
         <v>46164</v>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Brentwood Country Club</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D69" t="n">
         <v>1</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E69" t="n">
         <v>2</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F69" t="n">
         <v>1</v>
       </c>
-      <c r="G68" t="n">
+      <c r="G69" t="n">
         <v>1.417</v>
       </c>
-      <c r="H68" t="n">
+      <c r="H69" t="n">
         <v>0.011</v>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>Solid Finish</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Tyler</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Bethpage Green</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-1.167</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>

--- a/clutch_score_analysis.xlsx
+++ b/clutch_score_analysis.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1357,31 +1357,31 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45048</v>
+        <v>46185</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.333</v>
+        <v>1.867</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>2.183</v>
+        <v>1.517</v>
       </c>
       <c r="H27" t="n">
-        <v>0.01</v>
+        <v>-0.095</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1396,27 +1396,27 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45050</v>
+        <v>45048</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.067</v>
+        <v>1.333</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>1.556</v>
+        <v>2.183</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.023</v>
+        <v>0.01</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45053</v>
+        <v>45050</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1442,20 +1442,20 @@
         <v>1.067</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.8</v>
+        <v>1.2</v>
       </c>
       <c r="G29" t="n">
-        <v>-2.361</v>
+        <v>1.556</v>
       </c>
       <c r="H29" t="n">
-        <v>0.098</v>
+        <v>-0.023</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1470,27 +1470,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bethpage Yellow</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.4</v>
+        <v>1.067</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>2.2</v>
+        <v>-1.8</v>
       </c>
       <c r="G30" t="n">
-        <v>2.939</v>
+        <v>-2.361</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.079</v>
+        <v>0.098</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -1501,27 +1501,27 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45084</v>
+        <v>45053</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Bethpage Yellow</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1.133</v>
+        <v>1.4</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="G31" t="n">
-        <v>1.733</v>
+        <v>2.939</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.055</v>
+        <v>-0.079</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1536,31 +1536,31 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45137</v>
+        <v>45084</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bethpage Yellow</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.133</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="G32" t="n">
-        <v>1.283</v>
+        <v>1.733</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.006</v>
+        <v>-0.055</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45143</v>
+        <v>45137</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1579,23 +1579,23 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1.067</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="G33" t="n">
-        <v>2.65</v>
+        <v>1.283</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.006</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -1606,31 +1606,31 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45144</v>
+        <v>45143</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bethpage Black</t>
+          <t>Bethpage Yellow</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1.6</v>
+        <v>1.067</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="G34" t="n">
-        <v>1.433</v>
+        <v>2.65</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.06</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1641,31 +1641,31 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45156</v>
+        <v>45144</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Middle Island Country Club - Oak and Spruce</t>
+          <t>Bethpage Black</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1.267</v>
+        <v>1.6</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="G35" t="n">
-        <v>3.972</v>
+        <v>1.433</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.062</v>
+        <v>-0.06</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -1676,31 +1676,31 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45172</v>
+        <v>45156</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Middle Island Country Club - Oak and Spruce</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.8</v>
+        <v>1.267</v>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.6</v>
+        <v>2.8</v>
       </c>
       <c r="G36" t="n">
-        <v>-2.111</v>
+        <v>3.972</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.014</v>
+        <v>-0.062</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1711,31 +1711,31 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45434</v>
+        <v>45172</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bethpage Yellow</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="G37" t="n">
-        <v>0.161</v>
+        <v>-2.111</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.014</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45440</v>
+        <v>45434</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1754,23 +1754,23 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1.067</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>2.939</v>
+        <v>0.161</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.04</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1781,27 +1781,27 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45443</v>
+        <v>45440</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Yellow</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1.133</v>
+        <v>1.067</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="G39" t="n">
-        <v>4.128</v>
+        <v>2.939</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1816,31 +1816,31 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45453</v>
+        <v>45443</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1.333</v>
+        <v>1.133</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="G40" t="n">
-        <v>0.239</v>
+        <v>4.128</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.025</v>
+        <v>-0.09</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1851,31 +1851,31 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45465</v>
+        <v>45453</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.367</v>
+        <v>0.239</v>
       </c>
       <c r="H41" t="n">
-        <v>0.022</v>
+        <v>-0.025</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1886,31 +1886,31 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45466</v>
+        <v>45465</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bethpage Red</t>
+          <t>Wind Watch Hamlet Course</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.667</v>
+        <v>1.4</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>-1.8</v>
       </c>
       <c r="G42" t="n">
-        <v>1.383</v>
+        <v>-2.367</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.011</v>
+        <v>0.022</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -1921,31 +1921,31 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45467</v>
+        <v>45466</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Bethpage Red</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.533</v>
+        <v>0.667</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>2.033</v>
+        <v>1.383</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.011</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45475</v>
+        <v>45467</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1964,23 +1964,23 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.2</v>
+        <v>0.533</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.4</v>
+        <v>1.6</v>
       </c>
       <c r="G44" t="n">
-        <v>-1.517</v>
+        <v>2.033</v>
       </c>
       <c r="H44" t="n">
-        <v>0.024</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1991,31 +1991,31 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45480</v>
+        <v>45475</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bethpage Red</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.667</v>
+        <v>0.2</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>-1.4</v>
       </c>
       <c r="G45" t="n">
-        <v>2.494</v>
+        <v>-1.517</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.039</v>
+        <v>0.024</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2026,31 +2026,31 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45487</v>
+        <v>45480</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Red</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.017</v>
+        <v>2.494</v>
       </c>
       <c r="H46" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.039</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -2061,31 +2061,31 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45492</v>
+        <v>45487</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brentwood Country Club</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="G47" t="n">
-        <v>1.35</v>
+        <v>-0.017</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.018</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>45496</v>
+        <v>45492</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2104,23 +2104,23 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.467</v>
+        <v>0.667</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>1.783</v>
+        <v>1.35</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.011</v>
+        <v>-0.018</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2131,31 +2131,31 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>45502</v>
+        <v>45496</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Brentwood Country Club</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.533</v>
+        <v>0.467</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>-2.4</v>
+        <v>1.4</v>
       </c>
       <c r="G49" t="n">
-        <v>-3.428</v>
+        <v>1.783</v>
       </c>
       <c r="H49" t="n">
-        <v>0.054</v>
+        <v>-0.011</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -2166,31 +2166,31 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>45514</v>
+        <v>45502</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brentwood Country Club</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.867</v>
+        <v>0.533</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F50" t="n">
-        <v>2.6</v>
+        <v>-2.4</v>
       </c>
       <c r="G50" t="n">
-        <v>3.278</v>
+        <v>-3.428</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.054</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2201,31 +2201,31 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45535</v>
+        <v>45514</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bethpage Yellow</t>
+          <t>Brentwood Country Club</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.867</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="G51" t="n">
-        <v>1.011</v>
+        <v>3.278</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.05</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -2236,31 +2236,31 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>45570</v>
+        <v>45535</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Yellow</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.4</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E52" t="n">
         <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.8</v>
+        <v>0.8</v>
       </c>
       <c r="G52" t="n">
-        <v>-1.1</v>
+        <v>1.011</v>
       </c>
       <c r="H52" t="n">
-        <v>0.035</v>
+        <v>-0.05</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2271,31 +2271,31 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45580</v>
+        <v>45570</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sebonack Golf Club</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>-0.8</v>
       </c>
       <c r="G53" t="n">
-        <v>1.056</v>
+        <v>-1.1</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.013</v>
+        <v>0.035</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2306,31 +2306,31 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45649</v>
+        <v>45580</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ka'anapali Golf Resort Royal Course</t>
+          <t>Sebonack Golf Club</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.289</v>
+        <v>1.056</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.028</v>
+        <v>-0.013</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2341,31 +2341,31 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>45653</v>
+        <v>45649</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Ka'anapali Golf Resort Royal Course</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.4</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.844</v>
+        <v>-0.289</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.012</v>
+        <v>-0.028</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2376,31 +2376,31 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>45655</v>
+        <v>45653</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
-        <v>1.4</v>
+        <v>-0.8</v>
       </c>
       <c r="G56" t="n">
-        <v>1.989</v>
+        <v>-0.844</v>
       </c>
       <c r="H56" t="n">
-        <v>0.003</v>
+        <v>-0.012</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2411,31 +2411,31 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>45735</v>
+        <v>45655</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.333</v>
+        <v>0.8</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G57" t="n">
-        <v>1.189</v>
+        <v>1.989</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.051</v>
+        <v>0.003</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -2446,27 +2446,27 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>45829</v>
+        <v>45735</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brentwood Country Club</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.267</v>
+        <v>0.333</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>0.911</v>
+        <v>1.189</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.033</v>
+        <v>-0.051</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2481,27 +2481,27 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>45831</v>
+        <v>45829</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Brentwood Country Club</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.4</v>
+        <v>0.267</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="G59" t="n">
-        <v>1.483</v>
+        <v>0.911</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.068</v>
+        <v>-0.033</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -2516,27 +2516,27 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>45844</v>
+        <v>45831</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="G60" t="n">
-        <v>0.628</v>
+        <v>1.483</v>
       </c>
       <c r="H60" t="n">
-        <v>0.027</v>
+        <v>-0.068</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>45857</v>
+        <v>45844</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2559,23 +2559,23 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.2</v>
+        <v>0.467</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.433</v>
+        <v>0.628</v>
       </c>
       <c r="H61" t="n">
-        <v>0.002</v>
+        <v>0.027</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2586,31 +2586,31 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>45868</v>
+        <v>45857</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bethpage Red</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.667</v>
+        <v>0.2</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>-0.4</v>
       </c>
       <c r="G62" t="n">
-        <v>1.439</v>
+        <v>-0.433</v>
       </c>
       <c r="H62" t="n">
-        <v>0.018</v>
+        <v>0.002</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2621,31 +2621,31 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>45886</v>
+        <v>45868</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spring Lake Thunderbird</t>
+          <t>Bethpage Red</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.2</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.644</v>
+        <v>1.439</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.005</v>
+        <v>0.018</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>45892</v>
+        <v>45886</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2664,23 +2664,23 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.733</v>
+        <v>0.6</v>
       </c>
       <c r="E64" t="n">
         <v>2</v>
       </c>
       <c r="F64" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="G64" t="n">
-        <v>0.361</v>
+        <v>-0.644</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.055</v>
+        <v>-0.005</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2691,31 +2691,31 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>45894</v>
+        <v>45892</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1.2</v>
+        <v>0.733</v>
       </c>
       <c r="E65" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>-2.4</v>
+        <v>0.2</v>
       </c>
       <c r="G65" t="n">
-        <v>-2.606</v>
+        <v>0.361</v>
       </c>
       <c r="H65" t="n">
-        <v>0.068</v>
+        <v>-0.055</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2726,27 +2726,27 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>45897</v>
+        <v>45894</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spring Lake Thunderbird</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.867</v>
+        <v>1.2</v>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.4</v>
+        <v>-2.4</v>
       </c>
       <c r="G66" t="n">
-        <v>-1.789</v>
+        <v>-2.606</v>
       </c>
       <c r="H66" t="n">
-        <v>0.001</v>
+        <v>0.068</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -2761,27 +2761,27 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>45941</v>
+        <v>45897</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.867</v>
       </c>
       <c r="E67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F67" t="n">
-        <v>-2.2</v>
+        <v>-1.4</v>
       </c>
       <c r="G67" t="n">
-        <v>-2.9</v>
+        <v>-1.789</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -2796,27 +2796,27 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46160</v>
+        <v>45941</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Wind Watch Hamlet Course</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.467</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.6</v>
+        <v>-2.2</v>
       </c>
       <c r="G68" t="n">
-        <v>-1.972</v>
+        <v>-2.9</v>
       </c>
       <c r="H68" t="n">
-        <v>0.029</v>
+        <v>-0.001</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -2831,31 +2831,31 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brentwood Country Club</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>0.467</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>-1.6</v>
       </c>
       <c r="G69" t="n">
-        <v>1.417</v>
+        <v>-1.972</v>
       </c>
       <c r="H69" t="n">
-        <v>0.011</v>
+        <v>0.029</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2866,29 +2866,64 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Brentwood Country Club</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Solid Finish</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Tyler</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
         <v>46173</v>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Bethpage Green</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D71" t="n">
         <v>0.733</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E71" t="n">
         <v>3</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F71" t="n">
         <v>-0.8</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G71" t="n">
         <v>-1.167</v>
       </c>
-      <c r="H70" t="n">
+      <c r="H71" t="n">
         <v>0.023</v>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>Drop-off</t>
         </is>

--- a/clutch_score_analysis.xlsx
+++ b/clutch_score_analysis.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,35 +1147,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Rich</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45453</v>
+        <v>46201</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="E21" t="n">
         <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6</v>
+        <v>-1.4</v>
       </c>
       <c r="G21" t="n">
-        <v>2.556</v>
+        <v>-2.678</v>
       </c>
       <c r="H21" t="n">
-        <v>0.027</v>
+        <v>0.003</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -1186,27 +1186,27 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45492</v>
+        <v>45453</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brentwood Country Club</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.067</v>
+        <v>2.2</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="G22" t="n">
-        <v>5.894</v>
+        <v>2.556</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.122</v>
+        <v>0.027</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1221,31 +1221,31 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45520</v>
+        <v>45492</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Middle Island Country Club - Oak and Spruce</t>
+          <t>Brentwood Country Club</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1.4</v>
+        <v>2.067</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8</v>
+        <v>5.2</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.139</v>
+        <v>5.894</v>
       </c>
       <c r="H23" t="n">
-        <v>0.046</v>
+        <v>-0.122</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1256,31 +1256,31 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45765</v>
+        <v>45520</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cherry Creek</t>
+          <t>Middle Island Country Club - Oak and Spruce</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
-        <v>3.2</v>
+        <v>-1.8</v>
       </c>
       <c r="G24" t="n">
-        <v>3.817</v>
+        <v>-2.139</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.105</v>
+        <v>0.046</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -1291,31 +1291,31 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45853</v>
+        <v>45765</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pine Hollow</t>
+          <t>Cherry Creek</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2.067</v>
+        <v>2.4</v>
       </c>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8</v>
+        <v>3.2</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.25</v>
+        <v>3.817</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.014</v>
+        <v>-0.105</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1326,31 +1326,31 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45894</v>
+        <v>45853</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Pine Hollow</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2.4</v>
+        <v>2.067</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F26" t="n">
-        <v>2.2</v>
+        <v>-0.8</v>
       </c>
       <c r="G26" t="n">
-        <v>3.3</v>
+        <v>-1.25</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.046</v>
+        <v>-0.014</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -1361,27 +1361,27 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46185</v>
+        <v>45894</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.867</v>
+        <v>2.4</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="G27" t="n">
-        <v>1.517</v>
+        <v>3.3</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.095</v>
+        <v>-0.046</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1392,31 +1392,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45048</v>
+        <v>46185</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.333</v>
+        <v>1.867</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="G28" t="n">
-        <v>2.183</v>
+        <v>1.517</v>
       </c>
       <c r="H28" t="n">
-        <v>0.01</v>
+        <v>-0.095</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1427,31 +1427,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45050</v>
+        <v>46204</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1.067</v>
+        <v>1.6</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="G29" t="n">
-        <v>1.556</v>
+        <v>2.356</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.023</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1466,31 +1466,31 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45053</v>
+        <v>45048</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.067</v>
+        <v>1.333</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.8</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>-2.361</v>
+        <v>2.183</v>
       </c>
       <c r="H30" t="n">
-        <v>0.098</v>
+        <v>0.01</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1501,27 +1501,27 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45053</v>
+        <v>45050</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bethpage Yellow</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1.4</v>
+        <v>1.067</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="G31" t="n">
-        <v>2.939</v>
+        <v>1.556</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.079</v>
+        <v>-0.023</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1536,31 +1536,31 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45084</v>
+        <v>45053</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.133</v>
+        <v>1.067</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F32" t="n">
-        <v>1.4</v>
+        <v>-1.8</v>
       </c>
       <c r="G32" t="n">
-        <v>1.733</v>
+        <v>-2.361</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.055</v>
+        <v>0.098</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45137</v>
+        <v>45053</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1579,23 +1579,23 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="E33" t="n">
         <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="G33" t="n">
-        <v>1.283</v>
+        <v>2.939</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.006</v>
+        <v>-0.079</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1606,27 +1606,27 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45143</v>
+        <v>45084</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bethpage Yellow</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1.067</v>
+        <v>1.133</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="G34" t="n">
-        <v>2.65</v>
+        <v>1.733</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.055</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1641,27 +1641,27 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45144</v>
+        <v>45137</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bethpage Black</t>
+          <t>Bethpage Yellow</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1.6</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
         <v>0.8</v>
       </c>
       <c r="G35" t="n">
-        <v>1.433</v>
+        <v>1.283</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.06</v>
+        <v>-0.006</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1676,27 +1676,27 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45156</v>
+        <v>45143</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Middle Island Country Club - Oak and Spruce</t>
+          <t>Bethpage Yellow</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1.267</v>
+        <v>1.067</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="G36" t="n">
-        <v>3.972</v>
+        <v>2.65</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.062</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1711,31 +1711,31 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45172</v>
+        <v>45144</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Black</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="E37" t="n">
         <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.6</v>
+        <v>0.8</v>
       </c>
       <c r="G37" t="n">
-        <v>-2.111</v>
+        <v>1.433</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.014</v>
+        <v>-0.06</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -1746,31 +1746,31 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45434</v>
+        <v>45156</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bethpage Yellow</t>
+          <t>Middle Island Country Club - Oak and Spruce</t>
         </is>
       </c>
       <c r="D38" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="E38" t="n">
         <v>1</v>
       </c>
-      <c r="E38" t="n">
-        <v>3</v>
-      </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="G38" t="n">
-        <v>0.161</v>
+        <v>3.972</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.062</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1781,31 +1781,31 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45440</v>
+        <v>45172</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bethpage Yellow</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1.067</v>
+        <v>0.8</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F39" t="n">
-        <v>2.2</v>
+        <v>-1.6</v>
       </c>
       <c r="G39" t="n">
-        <v>2.939</v>
+        <v>-2.111</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.04</v>
+        <v>-0.014</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -1816,31 +1816,31 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45443</v>
+        <v>45434</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Yellow</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1.133</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" t="n">
         <v>0</v>
       </c>
-      <c r="F40" t="n">
-        <v>3.4</v>
-      </c>
       <c r="G40" t="n">
-        <v>4.128</v>
+        <v>0.161</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.09</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1851,31 +1851,31 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45453</v>
+        <v>45440</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Bethpage Yellow</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1.333</v>
+        <v>1.067</v>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="G41" t="n">
-        <v>0.239</v>
+        <v>2.939</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.025</v>
+        <v>-0.04</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1886,31 +1886,31 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45465</v>
+        <v>45443</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1.4</v>
+        <v>1.133</v>
       </c>
       <c r="E42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.8</v>
+        <v>3.4</v>
       </c>
       <c r="G42" t="n">
-        <v>-2.367</v>
+        <v>4.128</v>
       </c>
       <c r="H42" t="n">
-        <v>0.022</v>
+        <v>-0.09</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1921,31 +1921,31 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45466</v>
+        <v>45453</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bethpage Red</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.667</v>
+        <v>1.333</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>1.383</v>
+        <v>0.239</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.011</v>
+        <v>-0.025</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1956,31 +1956,31 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45467</v>
+        <v>45465</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Wind Watch Hamlet Course</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.533</v>
+        <v>1.4</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>1.6</v>
+        <v>-1.8</v>
       </c>
       <c r="G44" t="n">
-        <v>2.033</v>
+        <v>-2.367</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.022</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -1991,31 +1991,31 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45475</v>
+        <v>45466</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Bethpage Red</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.2</v>
+        <v>0.667</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.4</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.517</v>
+        <v>1.383</v>
       </c>
       <c r="H45" t="n">
-        <v>0.024</v>
+        <v>-0.011</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2026,27 +2026,27 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45480</v>
+        <v>45467</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bethpage Red</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.667</v>
+        <v>0.533</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="G46" t="n">
-        <v>2.494</v>
+        <v>2.033</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.039</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2061,31 +2061,31 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45487</v>
+        <v>45475</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2</v>
+        <v>-1.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.017</v>
+        <v>-1.517</v>
       </c>
       <c r="H47" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.024</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2096,31 +2096,31 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>45492</v>
+        <v>45480</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brentwood Country Club</t>
+          <t>Bethpage Red</t>
         </is>
       </c>
       <c r="D48" t="n">
         <v>0.667</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" t="n">
-        <v>1.35</v>
+        <v>2.494</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.018</v>
+        <v>-0.039</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -2131,31 +2131,31 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>45496</v>
+        <v>45487</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brentwood Country Club</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="G49" t="n">
-        <v>1.783</v>
+        <v>-0.017</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.011</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2166,31 +2166,31 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>45502</v>
+        <v>45492</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Brentwood Country Club</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.533</v>
+        <v>0.667</v>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.4</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>-3.428</v>
+        <v>1.35</v>
       </c>
       <c r="H50" t="n">
-        <v>0.054</v>
+        <v>-0.018</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45514</v>
+        <v>45496</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2209,19 +2209,19 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.867</v>
+        <v>0.467</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="G51" t="n">
-        <v>3.278</v>
+        <v>1.783</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.011</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2236,31 +2236,31 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>45535</v>
+        <v>45502</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bethpage Yellow</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.533</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8</v>
+        <v>-2.4</v>
       </c>
       <c r="G52" t="n">
-        <v>1.011</v>
+        <v>-3.428</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.05</v>
+        <v>0.054</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2271,31 +2271,31 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45570</v>
+        <v>45514</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Brentwood Country Club</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.4</v>
+        <v>0.867</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.8</v>
+        <v>2.6</v>
       </c>
       <c r="G53" t="n">
-        <v>-1.1</v>
+        <v>3.278</v>
       </c>
       <c r="H53" t="n">
-        <v>0.035</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -2306,27 +2306,27 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45580</v>
+        <v>45535</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sebonack Golf Club</t>
+          <t>Bethpage Yellow</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.667</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G54" t="n">
-        <v>1.056</v>
+        <v>1.011</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.013</v>
+        <v>-0.05</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2341,31 +2341,31 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>45649</v>
+        <v>45570</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ka'anapali Golf Resort Royal Course</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.289</v>
+        <v>-1.1</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.028</v>
+        <v>0.035</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2376,31 +2376,31 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>45653</v>
+        <v>45580</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Sebonack Golf Club</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.8</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.844</v>
+        <v>1.056</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.012</v>
+        <v>-0.013</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2411,31 +2411,31 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>45655</v>
+        <v>45649</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Ka'anapali Golf Resort Royal Course</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.8</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
-        <v>1.4</v>
+        <v>-0.2</v>
       </c>
       <c r="G57" t="n">
-        <v>1.989</v>
+        <v>-0.289</v>
       </c>
       <c r="H57" t="n">
-        <v>0.003</v>
+        <v>-0.028</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2446,31 +2446,31 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>45735</v>
+        <v>45653</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>-0.8</v>
       </c>
       <c r="G58" t="n">
-        <v>1.189</v>
+        <v>-0.844</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.051</v>
+        <v>-0.012</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2481,31 +2481,31 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>45829</v>
+        <v>45655</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brentwood Country Club</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.267</v>
+        <v>0.8</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="G59" t="n">
-        <v>0.911</v>
+        <v>1.989</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.033</v>
+        <v>0.003</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -2516,27 +2516,27 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>45831</v>
+        <v>45735</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>1.483</v>
+        <v>1.189</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.068</v>
+        <v>-0.051</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2551,27 +2551,27 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>45844</v>
+        <v>45829</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Brentwood Country Club</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.467</v>
+        <v>0.267</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="G61" t="n">
-        <v>0.628</v>
+        <v>0.911</v>
       </c>
       <c r="H61" t="n">
-        <v>0.027</v>
+        <v>-0.033</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2586,31 +2586,31 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>45857</v>
+        <v>45831</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.4</v>
+        <v>1.2</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.433</v>
+        <v>1.483</v>
       </c>
       <c r="H62" t="n">
-        <v>0.002</v>
+        <v>-0.068</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2621,27 +2621,27 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>45868</v>
+        <v>45844</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bethpage Red</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.667</v>
+        <v>0.467</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G63" t="n">
-        <v>1.439</v>
+        <v>0.628</v>
       </c>
       <c r="H63" t="n">
-        <v>0.018</v>
+        <v>0.027</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -2656,31 +2656,31 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>45886</v>
+        <v>45857</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spring Lake Thunderbird</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.644</v>
+        <v>-0.433</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.005</v>
+        <v>0.002</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2691,31 +2691,31 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>45892</v>
+        <v>45868</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spring Lake Thunderbird</t>
+          <t>Bethpage Red</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.733</v>
+        <v>0.667</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0.361</v>
+        <v>1.439</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.055</v>
+        <v>0.018</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2726,27 +2726,27 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>45894</v>
+        <v>45886</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="E66" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F66" t="n">
-        <v>-2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="G66" t="n">
-        <v>-2.606</v>
+        <v>-0.644</v>
       </c>
       <c r="H66" t="n">
-        <v>0.068</v>
+        <v>-0.005</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>45897</v>
+        <v>45892</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2769,23 +2769,23 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.867</v>
+        <v>0.733</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.4</v>
+        <v>0.2</v>
       </c>
       <c r="G67" t="n">
-        <v>-1.789</v>
+        <v>0.361</v>
       </c>
       <c r="H67" t="n">
-        <v>0.001</v>
+        <v>-0.055</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2796,27 +2796,27 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>45941</v>
+        <v>45894</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="E68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F68" t="n">
-        <v>-2.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G68" t="n">
-        <v>-2.9</v>
+        <v>-2.606</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.001</v>
+        <v>0.068</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -2831,27 +2831,27 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46160</v>
+        <v>45897</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.467</v>
+        <v>0.867</v>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.6</v>
+        <v>-1.4</v>
       </c>
       <c r="G69" t="n">
-        <v>-1.972</v>
+        <v>-1.789</v>
       </c>
       <c r="H69" t="n">
-        <v>0.029</v>
+        <v>0.001</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -2866,31 +2866,31 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46164</v>
+        <v>45941</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brentwood Country Club</t>
+          <t>Wind Watch Hamlet Course</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>-2.2</v>
       </c>
       <c r="G70" t="n">
-        <v>1.417</v>
+        <v>-2.9</v>
       </c>
       <c r="H70" t="n">
-        <v>0.011</v>
+        <v>-0.001</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2901,29 +2901,134 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46173</v>
+        <v>46160</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.733</v>
+        <v>0.467</v>
       </c>
       <c r="E71" t="n">
         <v>3</v>
       </c>
       <c r="F71" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-1.972</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Tyler</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Brentwood Country Club</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Solid Finish</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Tyler</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Bethpage Green</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3</v>
+      </c>
+      <c r="F73" t="n">
         <v>-0.8</v>
       </c>
-      <c r="G71" t="n">
+      <c r="G73" t="n">
         <v>-1.167</v>
       </c>
-      <c r="H71" t="n">
+      <c r="H73" t="n">
         <v>0.023</v>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Tyler</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Spring Lake Thunderbird</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="E74" t="n">
+        <v>6</v>
+      </c>
+      <c r="F74" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-3.983</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I74" t="inlineStr">
         <is>
           <t>Drop-off</t>
         </is>

--- a/clutch_score_analysis.xlsx
+++ b/clutch_score_analysis.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1462,31 +1462,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45048</v>
+        <v>46211</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Baiting Hollow</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.333</v>
+        <v>2.667</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>2.183</v>
+        <v>4.2</v>
       </c>
       <c r="H30" t="n">
-        <v>0.01</v>
+        <v>-0.102</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1501,27 +1501,27 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45050</v>
+        <v>45048</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1.067</v>
+        <v>1.333</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>1.556</v>
+        <v>2.183</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.023</v>
+        <v>0.01</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45053</v>
+        <v>45050</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1547,20 +1547,20 @@
         <v>1.067</v>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.8</v>
+        <v>1.2</v>
       </c>
       <c r="G32" t="n">
-        <v>-2.361</v>
+        <v>1.556</v>
       </c>
       <c r="H32" t="n">
-        <v>0.098</v>
+        <v>-0.023</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1575,27 +1575,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bethpage Yellow</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1.4</v>
+        <v>1.067</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F33" t="n">
-        <v>2.2</v>
+        <v>-1.8</v>
       </c>
       <c r="G33" t="n">
-        <v>2.939</v>
+        <v>-2.361</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.079</v>
+        <v>0.098</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -1606,27 +1606,27 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45084</v>
+        <v>45053</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Bethpage Yellow</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1.133</v>
+        <v>1.4</v>
       </c>
       <c r="E34" t="n">
         <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="G34" t="n">
-        <v>1.733</v>
+        <v>2.939</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.055</v>
+        <v>-0.079</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1641,31 +1641,31 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45137</v>
+        <v>45084</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bethpage Yellow</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.133</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="G35" t="n">
-        <v>1.283</v>
+        <v>1.733</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.006</v>
+        <v>-0.055</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45143</v>
+        <v>45137</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1684,23 +1684,23 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1.067</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="G36" t="n">
-        <v>2.65</v>
+        <v>1.283</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.006</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -1711,31 +1711,31 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45144</v>
+        <v>45143</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bethpage Black</t>
+          <t>Bethpage Yellow</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.6</v>
+        <v>1.067</v>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="G37" t="n">
-        <v>1.433</v>
+        <v>2.65</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.06</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1746,31 +1746,31 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45156</v>
+        <v>45144</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Middle Island Country Club - Oak and Spruce</t>
+          <t>Bethpage Black</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1.267</v>
+        <v>1.6</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F38" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="G38" t="n">
-        <v>3.972</v>
+        <v>1.433</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.062</v>
+        <v>-0.06</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -1781,31 +1781,31 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45172</v>
+        <v>45156</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Middle Island Country Club - Oak and Spruce</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.8</v>
+        <v>1.267</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.6</v>
+        <v>2.8</v>
       </c>
       <c r="G39" t="n">
-        <v>-2.111</v>
+        <v>3.972</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.014</v>
+        <v>-0.062</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1816,31 +1816,31 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45434</v>
+        <v>45172</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bethpage Yellow</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="G40" t="n">
-        <v>0.161</v>
+        <v>-2.111</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.014</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45440</v>
+        <v>45434</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1859,23 +1859,23 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1.067</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>2.939</v>
+        <v>0.161</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.04</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1886,27 +1886,27 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45443</v>
+        <v>45440</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Yellow</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1.133</v>
+        <v>1.067</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="G42" t="n">
-        <v>4.128</v>
+        <v>2.939</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1921,31 +1921,31 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45453</v>
+        <v>45443</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1.333</v>
+        <v>1.133</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="G43" t="n">
-        <v>0.239</v>
+        <v>4.128</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.025</v>
+        <v>-0.09</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -1956,31 +1956,31 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45465</v>
+        <v>45453</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="E44" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>-2.367</v>
+        <v>0.239</v>
       </c>
       <c r="H44" t="n">
-        <v>0.022</v>
+        <v>-0.025</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1991,31 +1991,31 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45466</v>
+        <v>45465</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bethpage Red</t>
+          <t>Wind Watch Hamlet Course</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.667</v>
+        <v>1.4</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>-1.8</v>
       </c>
       <c r="G45" t="n">
-        <v>1.383</v>
+        <v>-2.367</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.011</v>
+        <v>0.022</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2026,31 +2026,31 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45467</v>
+        <v>45466</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Bethpage Red</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.533</v>
+        <v>0.667</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>2.033</v>
+        <v>1.383</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.011</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45475</v>
+        <v>45467</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2069,23 +2069,23 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.2</v>
+        <v>0.533</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.4</v>
+        <v>1.6</v>
       </c>
       <c r="G47" t="n">
-        <v>-1.517</v>
+        <v>2.033</v>
       </c>
       <c r="H47" t="n">
-        <v>0.024</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -2096,31 +2096,31 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>45480</v>
+        <v>45475</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bethpage Red</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.667</v>
+        <v>0.2</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>-1.4</v>
       </c>
       <c r="G48" t="n">
-        <v>2.494</v>
+        <v>-1.517</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.039</v>
+        <v>0.024</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2131,31 +2131,31 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>45487</v>
+        <v>45480</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Red</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.017</v>
+        <v>2.494</v>
       </c>
       <c r="H49" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.039</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -2166,31 +2166,31 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>45492</v>
+        <v>45487</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brentwood Country Club</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="G50" t="n">
-        <v>1.35</v>
+        <v>-0.017</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.018</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45496</v>
+        <v>45492</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2209,23 +2209,23 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.467</v>
+        <v>0.667</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>1.783</v>
+        <v>1.35</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.011</v>
+        <v>-0.018</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2236,31 +2236,31 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>45502</v>
+        <v>45496</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Brentwood Country Club</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.533</v>
+        <v>0.467</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>-2.4</v>
+        <v>1.4</v>
       </c>
       <c r="G52" t="n">
-        <v>-3.428</v>
+        <v>1.783</v>
       </c>
       <c r="H52" t="n">
-        <v>0.054</v>
+        <v>-0.011</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -2271,31 +2271,31 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45514</v>
+        <v>45502</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brentwood Country Club</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.867</v>
+        <v>0.533</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>2.6</v>
+        <v>-2.4</v>
       </c>
       <c r="G53" t="n">
-        <v>3.278</v>
+        <v>-3.428</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.054</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2306,31 +2306,31 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45535</v>
+        <v>45514</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bethpage Yellow</t>
+          <t>Brentwood Country Club</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.867</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="G54" t="n">
-        <v>1.011</v>
+        <v>3.278</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.05</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -2341,31 +2341,31 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>45570</v>
+        <v>45535</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Yellow</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.4</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E55" t="n">
         <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.8</v>
+        <v>0.8</v>
       </c>
       <c r="G55" t="n">
-        <v>-1.1</v>
+        <v>1.011</v>
       </c>
       <c r="H55" t="n">
-        <v>0.035</v>
+        <v>-0.05</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2376,31 +2376,31 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>45580</v>
+        <v>45570</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sebonack Golf Club</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>-0.8</v>
       </c>
       <c r="G56" t="n">
-        <v>1.056</v>
+        <v>-1.1</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.013</v>
+        <v>0.035</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2411,31 +2411,31 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>45649</v>
+        <v>45580</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ka'anapali Golf Resort Royal Course</t>
+          <t>Sebonack Golf Club</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.289</v>
+        <v>1.056</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.028</v>
+        <v>-0.013</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2446,31 +2446,31 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>45653</v>
+        <v>45649</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Ka'anapali Golf Resort Royal Course</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.4</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.844</v>
+        <v>-0.289</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.012</v>
+        <v>-0.028</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2481,31 +2481,31 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>45655</v>
+        <v>45653</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" t="n">
-        <v>1.4</v>
+        <v>-0.8</v>
       </c>
       <c r="G59" t="n">
-        <v>1.989</v>
+        <v>-0.844</v>
       </c>
       <c r="H59" t="n">
-        <v>0.003</v>
+        <v>-0.012</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Strong Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2516,31 +2516,31 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>45735</v>
+        <v>45655</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.333</v>
+        <v>0.8</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G60" t="n">
-        <v>1.189</v>
+        <v>1.989</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.051</v>
+        <v>0.003</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Strong Finish</t>
         </is>
       </c>
     </row>
@@ -2551,27 +2551,27 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>45829</v>
+        <v>45735</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brentwood Country Club</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.267</v>
+        <v>0.333</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.911</v>
+        <v>1.189</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.033</v>
+        <v>-0.051</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2586,27 +2586,27 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>45831</v>
+        <v>45829</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Brentwood Country Club</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.4</v>
+        <v>0.267</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="G62" t="n">
-        <v>1.483</v>
+        <v>0.911</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.068</v>
+        <v>-0.033</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -2621,27 +2621,27 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>45844</v>
+        <v>45831</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="G63" t="n">
-        <v>0.628</v>
+        <v>1.483</v>
       </c>
       <c r="H63" t="n">
-        <v>0.027</v>
+        <v>-0.068</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>45857</v>
+        <v>45844</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2664,23 +2664,23 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.2</v>
+        <v>0.467</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.433</v>
+        <v>0.628</v>
       </c>
       <c r="H64" t="n">
-        <v>0.002</v>
+        <v>0.027</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2691,31 +2691,31 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>45868</v>
+        <v>45857</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bethpage Red</t>
+          <t>Bethpage Green</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.667</v>
+        <v>0.2</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>-0.4</v>
       </c>
       <c r="G65" t="n">
-        <v>1.439</v>
+        <v>-0.433</v>
       </c>
       <c r="H65" t="n">
-        <v>0.018</v>
+        <v>0.002</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2726,31 +2726,31 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>45886</v>
+        <v>45868</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spring Lake Thunderbird</t>
+          <t>Bethpage Red</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.2</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.644</v>
+        <v>1.439</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.005</v>
+        <v>0.018</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>45892</v>
+        <v>45886</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2769,23 +2769,23 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.733</v>
+        <v>0.6</v>
       </c>
       <c r="E67" t="n">
         <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="G67" t="n">
-        <v>0.361</v>
+        <v>-0.644</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.055</v>
+        <v>-0.005</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2796,31 +2796,31 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>45894</v>
+        <v>45892</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1.2</v>
+        <v>0.733</v>
       </c>
       <c r="E68" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>-2.4</v>
+        <v>0.2</v>
       </c>
       <c r="G68" t="n">
-        <v>-2.606</v>
+        <v>0.361</v>
       </c>
       <c r="H68" t="n">
-        <v>0.068</v>
+        <v>-0.055</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2831,27 +2831,27 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>45897</v>
+        <v>45894</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spring Lake Thunderbird</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.867</v>
+        <v>1.2</v>
       </c>
       <c r="E69" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.4</v>
+        <v>-2.4</v>
       </c>
       <c r="G69" t="n">
-        <v>-1.789</v>
+        <v>-2.606</v>
       </c>
       <c r="H69" t="n">
-        <v>0.001</v>
+        <v>0.068</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -2866,27 +2866,27 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>45941</v>
+        <v>45897</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.867</v>
       </c>
       <c r="E70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F70" t="n">
-        <v>-2.2</v>
+        <v>-1.4</v>
       </c>
       <c r="G70" t="n">
-        <v>-2.9</v>
+        <v>-1.789</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -2901,27 +2901,27 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46160</v>
+        <v>45941</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bethpage Blue</t>
+          <t>Wind Watch Hamlet Course</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.467</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.6</v>
+        <v>-2.2</v>
       </c>
       <c r="G71" t="n">
-        <v>-1.972</v>
+        <v>-2.9</v>
       </c>
       <c r="H71" t="n">
-        <v>0.029</v>
+        <v>-0.001</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -2936,31 +2936,31 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brentwood Country Club</t>
+          <t>Bethpage Blue</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>0.467</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>-1.6</v>
       </c>
       <c r="G72" t="n">
-        <v>1.417</v>
+        <v>-1.972</v>
       </c>
       <c r="H72" t="n">
-        <v>0.011</v>
+        <v>0.029</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Solid Finish</t>
+          <t>Drop-off</t>
         </is>
       </c>
     </row>
@@ -2971,31 +2971,31 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46173</v>
+        <v>46164</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bethpage Green</t>
+          <t>Brentwood Country Club</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.733</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.8</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>-1.167</v>
+        <v>1.417</v>
       </c>
       <c r="H73" t="n">
-        <v>0.023</v>
+        <v>0.011</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Drop-off</t>
+          <t>Solid Finish</t>
         </is>
       </c>
     </row>
@@ -3006,29 +3006,99 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Bethpage Green</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="E74" t="n">
+        <v>3</v>
+      </c>
+      <c r="F74" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-1.167</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Tyler</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
         <v>46201</v>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Spring Lake Thunderbird</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D75" t="n">
         <v>1.067</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E75" t="n">
         <v>6</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F75" t="n">
         <v>-2.8</v>
       </c>
-      <c r="G74" t="n">
+      <c r="G75" t="n">
         <v>-3.983</v>
       </c>
-      <c r="H74" t="n">
+      <c r="H75" t="n">
         <v>0.002</v>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Tyler</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Brentwood Country Club</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E76" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-2.756</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="I76" t="inlineStr">
         <is>
           <t>Drop-off</t>
         </is>
